--- a/graphgeneration/Graph_RuleSheet.xlsx
+++ b/graphgeneration/Graph_RuleSheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halle\Dropbox\Projects\Guidelines\graphgeneration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halle\Dropbox\Projects\guidelines_urs\graphgeneration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E858461-A45D-47ED-87DC-B06F8388748F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EAD1B6-E575-4D53-8450-79AC3DD2670A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12168" yWindow="36" windowWidth="10872" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="182">
   <si>
     <t>Conceptual Size (L or S)</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Employment Rates</t>
-  </si>
-  <si>
     <t>Los Angeles</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>Aayush</t>
   </si>
   <si>
-    <t>Average Employment Rates</t>
-  </si>
-  <si>
     <t>0-100</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
     <t>Facebook</t>
   </si>
   <si>
-    <t>Footware Market Revenue</t>
-  </si>
-  <si>
     <t>Revenue in Billions (USD)</t>
   </si>
   <si>
@@ -549,10 +540,37 @@
     <t>Halle</t>
   </si>
   <si>
-    <t>Salmon_NonTrunc</t>
-  </si>
-  <si>
     <t>Salmon_Trunc</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>ExampleLitRate_NonTrunc</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Literacy Rate in Nicaragua and Portugal</t>
+  </si>
+  <si>
+    <t>This chart shows the literacy rate in Nicaragua and Portugal over different years.</t>
+  </si>
+  <si>
+    <t>Employment Rates in Los Angeles and Chicago</t>
+  </si>
+  <si>
+    <t>Employment Rates (percent)</t>
+  </si>
+  <si>
+    <t>Footwear Market Revenue</t>
+  </si>
+  <si>
+    <t>FootwearRev_NonTrunc_S_2</t>
+  </si>
+  <si>
+    <t>FootwearRev_Trunc_S_1</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1089,37 +1107,37 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -1127,22 +1145,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
       </c>
       <c r="H2" s="2">
         <v>2015</v>
@@ -1163,25 +1181,25 @@
         <v>95.6</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="R2" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1189,22 +1207,22 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2">
         <v>2010</v>
@@ -1225,25 +1243,25 @@
         <v>86</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1251,22 +1269,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
         <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
       </c>
       <c r="H4" s="2">
         <v>2019</v>
@@ -1287,25 +1305,25 @@
         <v>81</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1313,22 +1331,22 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H5" s="2">
         <v>2015</v>
@@ -1349,25 +1367,25 @@
         <v>74.08</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="O5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:22" s="16" customFormat="1" x14ac:dyDescent="0.3">
@@ -1375,28 +1393,28 @@
         <v>9</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="16" t="s">
+      <c r="I6" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="J6" s="16">
         <v>390</v>
@@ -1411,25 +1429,25 @@
         <v>378</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="R6" s="21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="U6" s="18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="V6" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -1437,22 +1455,22 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2">
         <v>1979</v>
@@ -1473,25 +1491,25 @@
         <v>50</v>
       </c>
       <c r="N7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:22" s="16" customFormat="1" x14ac:dyDescent="0.3">
@@ -1499,22 +1517,22 @@
         <v>9</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H8" s="17">
         <v>2010</v>
@@ -1535,25 +1553,25 @@
         <v>35</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="R8" s="21" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="V8" s="26" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:22" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1561,22 +1579,22 @@
         <v>9</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>10</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H9" s="17">
         <v>2018</v>
@@ -1597,48 +1615,48 @@
         <v>141.80000000000001</v>
       </c>
       <c r="N9" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="R9" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="O9" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q9" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="R9" s="21" t="s">
-        <v>156</v>
-      </c>
       <c r="U9" s="27" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="V9" s="28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2">
         <v>2006</v>
@@ -1659,48 +1677,48 @@
         <v>76.900000000000006</v>
       </c>
       <c r="N10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="R10" s="14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H11" s="2">
         <v>2015</v>
@@ -1721,48 +1739,48 @@
         <v>43</v>
       </c>
       <c r="N11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="V11" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:22" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H12" s="17">
         <v>2022</v>
@@ -1783,48 +1801,48 @@
         <v>51.585999999999999</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P12" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q12" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="R12" s="20" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="U12" s="25" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="V12" s="26" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H13" s="2">
         <v>2024</v>
@@ -1845,54 +1863,54 @@
         <v>95</v>
       </c>
       <c r="N13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="R13" s="14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="V13" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E14" t="s">
+      <c r="I14" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="J14">
         <v>77.400000000000006</v>
@@ -1907,48 +1925,48 @@
         <v>85.6</v>
       </c>
       <c r="N14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2">
         <v>2020</v>
@@ -1969,54 +1987,54 @@
         <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s">
         <v>68</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="J16">
         <v>49</v>
@@ -2031,48 +2049,48 @@
         <v>51</v>
       </c>
       <c r="N16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="V16" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H17" s="2">
         <v>2020</v>
@@ -2093,67 +2111,67 @@
         <v>86.92</v>
       </c>
       <c r="N17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="V17" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="N19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" t="s">
         <v>163</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
         <v>164</v>
       </c>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
         <v>165</v>
       </c>
-      <c r="E22" t="s">
+      <c r="H22" t="s">
         <v>166</v>
       </c>
-      <c r="F22" t="s">
+      <c r="I22" t="s">
         <v>167</v>
-      </c>
-      <c r="G22" t="s">
-        <v>168</v>
-      </c>
-      <c r="H22" t="s">
-        <v>169</v>
-      </c>
-      <c r="I22" t="s">
-        <v>170</v>
       </c>
       <c r="J22">
         <v>54</v>
@@ -2168,19 +2186,63 @@
         <v>59</v>
       </c>
       <c r="N22" t="s">
+        <v>168</v>
+      </c>
+      <c r="O22" t="s">
+        <v>169</v>
+      </c>
+      <c r="P22" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q22" t="s">
         <v>171</v>
       </c>
-      <c r="O22" t="s">
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" t="s">
         <v>172</v>
       </c>
-      <c r="P22" t="s">
+      <c r="H23">
+        <v>2005</v>
+      </c>
+      <c r="I23">
+        <v>2025</v>
+      </c>
+      <c r="J23">
+        <v>78</v>
+      </c>
+      <c r="K23">
+        <v>85</v>
+      </c>
+      <c r="L23">
+        <v>94</v>
+      </c>
+      <c r="M23">
+        <v>96</v>
+      </c>
+      <c r="N23" t="s">
+        <v>18</v>
+      </c>
+      <c r="P23" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q23" t="s">
         <v>173</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>174</v>
-      </c>
-      <c r="R22" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/graphgeneration/Graph_RuleSheet.xlsx
+++ b/graphgeneration/Graph_RuleSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halle\Dropbox\Projects\guidelines_urs\graphgeneration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EAD1B6-E575-4D53-8450-79AC3DD2670A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB24123-DE45-4ACE-BB48-071693B4D2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12168" yWindow="36" windowWidth="10872" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
